--- a/Assets/결과/#3 장애물 가운데 추가 및 사이즈 증가/Excel/TestControllerAgent_MissReward(Clone)1_vs_TestTotalAgent_Origin(Clone)2.xlsx
+++ b/Assets/결과/#3 장애물 가운데 추가 및 사이즈 증가/Excel/TestControllerAgent_MissReward(Clone)1_vs_TestTotalAgent_Origin(Clone)2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dltrn\Github\Unity-MLAgents-FPS\Assets\결과\#3 장애물 가운데 추가 및 사이즈 증가\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD8C876-5E70-4E34-81C6-D45F8033C666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02940919-2F19-46F3-BEA5-71F50E90326B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2388" yWindow="2952" windowWidth="17280" windowHeight="9960" xr2:uid="{8DE4F5E4-649C-4EFF-88EA-FA92F21E2AF0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8DE4F5E4-649C-4EFF-88EA-FA92F21E2AF0}"/>
   </bookViews>
   <sheets>
     <sheet name="TestControllerAgent_MissReward(" sheetId="1" r:id="rId1"/>
@@ -769,6 +769,13 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF44B3E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -793,13 +800,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF44B3E1"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -814,7 +814,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F1367FB-63B8-45F8-83D1-56B288F36BB5}" name="표1" displayName="표1" ref="A1:H2001" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F1367FB-63B8-45F8-83D1-56B288F36BB5}" name="표1" displayName="표1" ref="A1:H2001" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="0">
   <autoFilter ref="A1:H2001" xr:uid="{4F1367FB-63B8-45F8-83D1-56B288F36BB5}">
     <filterColumn colId="1">
       <filters>
